--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussFinBondRepInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussFinBondRepInfo.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\华夏\需求文档\需求确认材料\数据补录模板\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\huaxia\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13125" tabRatio="743"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13125" tabRatio="743" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="1339">
   <si>
     <t>公共信息（必填）</t>
   </si>
@@ -6026,6 +6026,27 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6033,18 +6054,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6071,28 +6080,40 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6105,15 +6126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -6121,18 +6133,6 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6645,8 +6645,12 @@
       <c r="S3" s="61"/>
       <c r="T3" s="61"/>
       <c r="U3" s="61"/>
-      <c r="V3" s="64"/>
-      <c r="W3" s="64"/>
+      <c r="V3" s="64" t="s">
+        <v>1261</v>
+      </c>
+      <c r="W3" s="64" t="s">
+        <v>1282</v>
+      </c>
       <c r="X3" s="64"/>
     </row>
     <row r="4" spans="1:24" s="60" customFormat="1">
@@ -6698,7 +6702,9 @@
       <c r="T5" s="61"/>
       <c r="U5" s="61"/>
       <c r="V5" s="64"/>
-      <c r="W5" s="64"/>
+      <c r="W5" s="64" t="s">
+        <v>1274</v>
+      </c>
       <c r="X5" s="64"/>
     </row>
     <row r="6" spans="1:24" s="60" customFormat="1">
@@ -6963,13 +6969,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="98"/>
+      <c r="B1" s="80"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="91" t="s">
         <v>43</v>
       </c>
       <c r="B2" s="29" t="s">
@@ -6977,25 +6983,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="89"/>
+      <c r="A3" s="92"/>
       <c r="B3" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="89"/>
+      <c r="A4" s="92"/>
       <c r="B4" s="26" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="90"/>
+      <c r="A5" s="93"/>
       <c r="B5" s="24" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="17" customFormat="1">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="94" t="s">
         <v>48</v>
       </c>
       <c r="B6" s="29" t="s">
@@ -7003,13 +7009,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="17" customFormat="1">
-      <c r="A7" s="92"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="23" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="17" customFormat="1">
-      <c r="A8" s="93" t="s">
+      <c r="A8" s="96" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="22" t="s">
@@ -7017,13 +7023,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="17" customFormat="1">
-      <c r="A9" s="92"/>
+      <c r="A9" s="95"/>
       <c r="B9" s="23" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="94" t="s">
+      <c r="A10" s="84" t="s">
         <v>54</v>
       </c>
       <c r="B10" s="26" t="s">
@@ -7031,61 +7037,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="95"/>
+      <c r="A11" s="97"/>
       <c r="B11" s="26" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="95"/>
+      <c r="A12" s="97"/>
       <c r="B12" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="95"/>
+      <c r="A13" s="97"/>
       <c r="B13" s="26" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="95"/>
+      <c r="A14" s="97"/>
       <c r="B14" s="26" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="95"/>
+      <c r="A15" s="97"/>
       <c r="B15" s="26" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="95"/>
+      <c r="A16" s="97"/>
       <c r="B16" s="26" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="95"/>
+      <c r="A17" s="97"/>
       <c r="B17" s="26" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="95"/>
+      <c r="A18" s="97"/>
       <c r="B18" s="26" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="95"/>
+      <c r="A19" s="97"/>
       <c r="B19" s="26" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="95"/>
+      <c r="A20" s="97"/>
       <c r="B20" s="26" t="s">
         <v>65</v>
       </c>
@@ -7099,7 +7105,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="94" t="s">
+      <c r="A22" s="84" t="s">
         <v>68</v>
       </c>
       <c r="B22" s="29" t="s">
@@ -7107,19 +7113,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="95"/>
+      <c r="A23" s="97"/>
       <c r="B23" s="26" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="96"/>
+      <c r="A24" s="85"/>
       <c r="B24" s="24" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="94" t="s">
+      <c r="A25" s="84" t="s">
         <v>72</v>
       </c>
       <c r="B25" s="26" t="s">
@@ -7127,67 +7133,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="95"/>
+      <c r="A26" s="97"/>
       <c r="B26" s="26" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="95"/>
+      <c r="A27" s="97"/>
       <c r="B27" s="21" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="95"/>
+      <c r="A28" s="97"/>
       <c r="B28" s="21" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="95"/>
+      <c r="A29" s="97"/>
       <c r="B29" s="21" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="95"/>
+      <c r="A30" s="97"/>
       <c r="B30" s="21" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="95"/>
+      <c r="A31" s="97"/>
       <c r="B31" s="21" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="95"/>
+      <c r="A32" s="97"/>
       <c r="B32" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="95"/>
+      <c r="A33" s="97"/>
       <c r="B33" s="21" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="95"/>
+      <c r="A34" s="97"/>
       <c r="B34" s="21" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="96"/>
+      <c r="A35" s="85"/>
       <c r="B35" s="41" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="94" t="s">
+      <c r="A36" s="84" t="s">
         <v>84</v>
       </c>
       <c r="B36" s="21" t="s">
@@ -7195,25 +7201,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="95"/>
+      <c r="A37" s="97"/>
       <c r="B37" s="26" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="95"/>
+      <c r="A38" s="97"/>
       <c r="B38" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="96"/>
+      <c r="A39" s="85"/>
       <c r="B39" s="21" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="94" t="s">
+      <c r="A40" s="84" t="s">
         <v>89</v>
       </c>
       <c r="B40" s="20" t="s">
@@ -7221,43 +7227,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="95"/>
+      <c r="A41" s="97"/>
       <c r="B41" s="21" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="95"/>
+      <c r="A42" s="97"/>
       <c r="B42" s="21" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="95"/>
+      <c r="A43" s="97"/>
       <c r="B43" s="21" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="95"/>
+      <c r="A44" s="97"/>
       <c r="B44" s="21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="95"/>
+      <c r="A45" s="97"/>
       <c r="B45" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="96"/>
+      <c r="A46" s="85"/>
       <c r="B46" s="24" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="94" t="s">
+      <c r="A47" s="84" t="s">
         <v>97</v>
       </c>
       <c r="B47" s="29" t="s">
@@ -7265,61 +7271,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="95"/>
+      <c r="A48" s="97"/>
       <c r="B48" s="21" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="95"/>
+      <c r="A49" s="97"/>
       <c r="B49" s="21" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="95"/>
+      <c r="A50" s="97"/>
       <c r="B50" s="21" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="95"/>
+      <c r="A51" s="97"/>
       <c r="B51" s="21" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="95"/>
+      <c r="A52" s="97"/>
       <c r="B52" s="21" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="95"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="26" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="95"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="21" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="95"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="26" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="96"/>
+      <c r="A56" s="85"/>
       <c r="B56" s="24" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="94" t="s">
+      <c r="A57" s="84" t="s">
         <v>108</v>
       </c>
       <c r="B57" s="20" t="s">
@@ -7327,19 +7333,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="95"/>
+      <c r="A58" s="97"/>
       <c r="B58" s="21" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="96"/>
+      <c r="A59" s="85"/>
       <c r="B59" s="24" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="94" t="s">
+      <c r="A60" s="84" t="s">
         <v>112</v>
       </c>
       <c r="B60" s="34" t="s">
@@ -7347,37 +7353,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="95"/>
+      <c r="A61" s="97"/>
       <c r="B61" s="21" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="95"/>
+      <c r="A62" s="97"/>
       <c r="B62" s="35" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="95"/>
+      <c r="A63" s="97"/>
       <c r="B63" s="21" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="95"/>
+      <c r="A64" s="97"/>
       <c r="B64" s="21" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="96"/>
+      <c r="A65" s="85"/>
       <c r="B65" s="28" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="94" t="s">
+      <c r="A66" s="84" t="s">
         <v>119</v>
       </c>
       <c r="B66" s="34" t="s">
@@ -7385,37 +7391,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="95"/>
+      <c r="A67" s="97"/>
       <c r="B67" s="21" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="95"/>
+      <c r="A68" s="97"/>
       <c r="B68" s="21" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="95"/>
+      <c r="A69" s="97"/>
       <c r="B69" s="21" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="95"/>
+      <c r="A70" s="97"/>
       <c r="B70" s="21" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="96"/>
+      <c r="A71" s="85"/>
       <c r="B71" s="28" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="17" customFormat="1">
-      <c r="A72" s="94" t="s">
+      <c r="A72" s="84" t="s">
         <v>126</v>
       </c>
       <c r="B72" s="21" t="s">
@@ -7423,103 +7429,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="17" customFormat="1">
-      <c r="A73" s="95"/>
+      <c r="A73" s="97"/>
       <c r="B73" s="21" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="17" customFormat="1">
-      <c r="A74" s="95"/>
+      <c r="A74" s="97"/>
       <c r="B74" s="21" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="17" customFormat="1">
-      <c r="A75" s="95"/>
+      <c r="A75" s="97"/>
       <c r="B75" s="21" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="17" customFormat="1">
-      <c r="A76" s="95"/>
+      <c r="A76" s="97"/>
       <c r="B76" s="21" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="17" customFormat="1">
-      <c r="A77" s="95"/>
+      <c r="A77" s="97"/>
       <c r="B77" s="36" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="17" customFormat="1">
-      <c r="A78" s="95"/>
+      <c r="A78" s="97"/>
       <c r="B78" s="21" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="17" customFormat="1">
-      <c r="A79" s="95"/>
+      <c r="A79" s="97"/>
       <c r="B79" s="21" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="17" customFormat="1">
-      <c r="A80" s="95"/>
+      <c r="A80" s="97"/>
       <c r="B80" s="21" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="17" customFormat="1">
-      <c r="A81" s="95"/>
+      <c r="A81" s="97"/>
       <c r="B81" s="36" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="17" customFormat="1">
-      <c r="A82" s="95"/>
+      <c r="A82" s="97"/>
       <c r="B82" s="21" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="17" customFormat="1">
-      <c r="A83" s="95"/>
+      <c r="A83" s="97"/>
       <c r="B83" s="21" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="17" customFormat="1">
-      <c r="A84" s="95"/>
+      <c r="A84" s="97"/>
       <c r="B84" s="21" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="17" customFormat="1">
-      <c r="A85" s="95"/>
+      <c r="A85" s="97"/>
       <c r="B85" s="36" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="17" customFormat="1">
-      <c r="A86" s="95"/>
+      <c r="A86" s="97"/>
       <c r="B86" s="36" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="17" customFormat="1">
-      <c r="A87" s="95"/>
+      <c r="A87" s="97"/>
       <c r="B87" s="36" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="17" customFormat="1">
-      <c r="A88" s="96"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="24" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="17" customFormat="1">
-      <c r="A89" s="94" t="s">
+      <c r="A89" s="84" t="s">
         <v>144</v>
       </c>
       <c r="B89" s="26" t="s">
@@ -7527,38 +7533,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="17" customFormat="1">
-      <c r="A90" s="95"/>
+      <c r="A90" s="97"/>
       <c r="B90" s="26" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="17" customFormat="1">
-      <c r="A91" s="95"/>
+      <c r="A91" s="97"/>
       <c r="B91" s="26" t="s">
         <v>147</v>
       </c>
       <c r="F91" s="42"/>
     </row>
     <row r="92" spans="1:6" s="17" customFormat="1">
-      <c r="A92" s="95"/>
+      <c r="A92" s="97"/>
       <c r="B92" s="43" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="17" customFormat="1">
-      <c r="A93" s="95"/>
+      <c r="A93" s="97"/>
       <c r="B93" s="26" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="17" customFormat="1">
-      <c r="A94" s="96"/>
+      <c r="A94" s="85"/>
       <c r="B94" s="24" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="17" customFormat="1">
-      <c r="A95" s="94" t="s">
+      <c r="A95" s="84" t="s">
         <v>151</v>
       </c>
       <c r="B95" s="37" t="s">
@@ -7566,43 +7572,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="17" customFormat="1">
-      <c r="A96" s="95"/>
+      <c r="A96" s="97"/>
       <c r="B96" s="36" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="17" customFormat="1">
-      <c r="A97" s="95"/>
+      <c r="A97" s="97"/>
       <c r="B97" s="36" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="17" customFormat="1">
-      <c r="A98" s="95"/>
+      <c r="A98" s="97"/>
       <c r="B98" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="17" customFormat="1">
-      <c r="A99" s="95"/>
+      <c r="A99" s="97"/>
       <c r="B99" s="36" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="17" customFormat="1">
-      <c r="A100" s="95"/>
+      <c r="A100" s="97"/>
       <c r="B100" s="36" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="17" customFormat="1">
-      <c r="A101" s="96"/>
+      <c r="A101" s="85"/>
       <c r="B101" s="32" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="17" customFormat="1">
-      <c r="A102" s="94" t="s">
+      <c r="A102" s="84" t="s">
         <v>159</v>
       </c>
       <c r="B102" s="20" t="s">
@@ -7610,7 +7616,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="17" customFormat="1">
-      <c r="A103" s="96"/>
+      <c r="A103" s="85"/>
       <c r="B103" s="24" t="s">
         <v>161</v>
       </c>
@@ -7628,10 +7634,10 @@
       <c r="B105" s="27"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="97" t="s">
+      <c r="A107" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="B107" s="98"/>
+      <c r="B107" s="80"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="47"/>
@@ -7802,17 +7808,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="82" t="s">
+      <c r="A137" s="98" t="s">
         <v>193</v>
       </c>
-      <c r="B137" s="83"/>
+      <c r="B137" s="99"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="84"/>
-      <c r="B138" s="85"/>
+      <c r="A138" s="100"/>
+      <c r="B138" s="101"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="79" t="s">
+      <c r="A139" s="86" t="s">
         <v>194</v>
       </c>
       <c r="B139" s="49" t="s">
@@ -7820,31 +7826,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="80"/>
+      <c r="A140" s="87"/>
       <c r="B140" s="50" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="80"/>
+      <c r="A141" s="87"/>
       <c r="B141" s="50" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="80"/>
+      <c r="A142" s="87"/>
       <c r="B142" s="50" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="81"/>
+      <c r="A143" s="88"/>
       <c r="B143" s="52" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="79" t="s">
+      <c r="A144" s="86" t="s">
         <v>200</v>
       </c>
       <c r="B144" s="49" t="s">
@@ -7852,43 +7858,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="80"/>
+      <c r="A145" s="87"/>
       <c r="B145" s="50" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="80"/>
+      <c r="A146" s="87"/>
       <c r="B146" s="50" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="80"/>
+      <c r="A147" s="87"/>
       <c r="B147" s="50" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="80"/>
+      <c r="A148" s="87"/>
       <c r="B148" s="50" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="80"/>
+      <c r="A149" s="87"/>
       <c r="B149" s="50" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="81"/>
+      <c r="A150" s="88"/>
       <c r="B150" s="52" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="79" t="s">
+      <c r="A151" s="86" t="s">
         <v>208</v>
       </c>
       <c r="B151" s="49" t="s">
@@ -7896,187 +7902,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="80"/>
+      <c r="A152" s="87"/>
       <c r="B152" s="50" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="80"/>
+      <c r="A153" s="87"/>
       <c r="B153" s="50" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="80"/>
+      <c r="A154" s="87"/>
       <c r="B154" s="50" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="80"/>
+      <c r="A155" s="87"/>
       <c r="B155" s="50" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="80"/>
+      <c r="A156" s="87"/>
       <c r="B156" s="50" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="80"/>
+      <c r="A157" s="87"/>
       <c r="B157" s="50" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="80"/>
+      <c r="A158" s="87"/>
       <c r="B158" s="50" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="80"/>
+      <c r="A159" s="87"/>
       <c r="B159" s="50" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="80"/>
+      <c r="A160" s="87"/>
       <c r="B160" s="50" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="80"/>
+      <c r="A161" s="87"/>
       <c r="B161" s="50" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="80"/>
+      <c r="A162" s="87"/>
       <c r="B162" s="50" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="80"/>
+      <c r="A163" s="87"/>
       <c r="B163" s="50" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="80"/>
+      <c r="A164" s="87"/>
       <c r="B164" s="50" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="80"/>
+      <c r="A165" s="87"/>
       <c r="B165" s="50" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="80"/>
+      <c r="A166" s="87"/>
       <c r="B166" s="50" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="80"/>
+      <c r="A167" s="87"/>
       <c r="B167" s="50" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="80"/>
+      <c r="A168" s="87"/>
       <c r="B168" s="50" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="80"/>
+      <c r="A169" s="87"/>
       <c r="B169" s="50" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="80"/>
+      <c r="A170" s="87"/>
       <c r="B170" s="50" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="80"/>
+      <c r="A171" s="87"/>
       <c r="B171" s="50" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="80"/>
+      <c r="A172" s="87"/>
       <c r="B172" s="50" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="80"/>
+      <c r="A173" s="87"/>
       <c r="B173" s="50" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="80"/>
+      <c r="A174" s="87"/>
       <c r="B174" s="50" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="80"/>
+      <c r="A175" s="87"/>
       <c r="B175" s="50" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="80"/>
+      <c r="A176" s="87"/>
       <c r="B176" s="50" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="80"/>
+      <c r="A177" s="87"/>
       <c r="B177" s="50" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="80"/>
+      <c r="A178" s="87"/>
       <c r="B178" s="50" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="80"/>
+      <c r="A179" s="87"/>
       <c r="B179" s="50" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="80"/>
+      <c r="A180" s="87"/>
       <c r="B180" s="50" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="81"/>
+      <c r="A181" s="88"/>
       <c r="B181" s="52" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="79" t="s">
+      <c r="A182" s="86" t="s">
         <v>240</v>
       </c>
       <c r="B182" s="49" t="s">
@@ -8084,19 +8090,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="80"/>
+      <c r="A183" s="87"/>
       <c r="B183" s="50" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="81"/>
+      <c r="A184" s="88"/>
       <c r="B184" s="52" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="79" t="s">
+      <c r="A185" s="86" t="s">
         <v>244</v>
       </c>
       <c r="B185" s="49" t="s">
@@ -8104,25 +8110,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="80"/>
+      <c r="A186" s="87"/>
       <c r="B186" s="50" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="80"/>
+      <c r="A187" s="87"/>
       <c r="B187" s="50" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="81"/>
+      <c r="A188" s="88"/>
       <c r="B188" s="52" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="79" t="s">
+      <c r="A189" s="86" t="s">
         <v>249</v>
       </c>
       <c r="B189" s="49" t="s">
@@ -8130,13 +8136,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="81"/>
+      <c r="A190" s="88"/>
       <c r="B190" s="52" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="79" t="s">
+      <c r="A191" s="86" t="s">
         <v>252</v>
       </c>
       <c r="B191" s="49" t="s">
@@ -8144,49 +8150,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="80"/>
+      <c r="A192" s="87"/>
       <c r="B192" s="50" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="80"/>
+      <c r="A193" s="87"/>
       <c r="B193" s="50" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="80"/>
+      <c r="A194" s="87"/>
       <c r="B194" s="50" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="80"/>
+      <c r="A195" s="87"/>
       <c r="B195" s="50" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="80"/>
+      <c r="A196" s="87"/>
       <c r="B196" s="50" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="80"/>
+      <c r="A197" s="87"/>
       <c r="B197" s="50" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="81"/>
+      <c r="A198" s="88"/>
       <c r="B198" s="52" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="79" t="s">
+      <c r="A199" s="86" t="s">
         <v>261</v>
       </c>
       <c r="B199" s="49" t="s">
@@ -8194,13 +8200,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="81"/>
+      <c r="A200" s="88"/>
       <c r="B200" s="52" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="79" t="s">
+      <c r="A201" s="86" t="s">
         <v>264</v>
       </c>
       <c r="B201" s="49" t="s">
@@ -8208,19 +8214,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="80"/>
+      <c r="A202" s="87"/>
       <c r="B202" s="50" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="81"/>
+      <c r="A203" s="88"/>
       <c r="B203" s="52" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="79" t="s">
+      <c r="A204" s="86" t="s">
         <v>268</v>
       </c>
       <c r="B204" s="49" t="s">
@@ -8228,19 +8234,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="80"/>
+      <c r="A205" s="87"/>
       <c r="B205" s="50" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="80"/>
+      <c r="A206" s="87"/>
       <c r="B206" s="50" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="81"/>
+      <c r="A207" s="88"/>
       <c r="B207" s="52" t="s">
         <v>272</v>
       </c>
@@ -8254,7 +8260,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="79" t="s">
+      <c r="A209" s="86" t="s">
         <v>275</v>
       </c>
       <c r="B209" s="49" t="s">
@@ -8262,13 +8268,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="81"/>
+      <c r="A210" s="88"/>
       <c r="B210" s="52" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="79" t="s">
+      <c r="A211" s="86" t="s">
         <v>278</v>
       </c>
       <c r="B211" s="49" t="s">
@@ -8276,19 +8282,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="80"/>
+      <c r="A212" s="87"/>
       <c r="B212" s="50" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="81"/>
+      <c r="A213" s="88"/>
       <c r="B213" s="52" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="79" t="s">
+      <c r="A214" s="86" t="s">
         <v>282</v>
       </c>
       <c r="B214" s="49" t="s">
@@ -8296,19 +8302,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="80"/>
+      <c r="A215" s="87"/>
       <c r="B215" s="50" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="81"/>
+      <c r="A216" s="88"/>
       <c r="B216" s="52" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="79" t="s">
+      <c r="A217" s="86" t="s">
         <v>286</v>
       </c>
       <c r="B217" s="49" t="s">
@@ -8316,13 +8322,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="80"/>
+      <c r="A218" s="87"/>
       <c r="B218" s="50" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="81"/>
+      <c r="A219" s="88"/>
       <c r="B219" s="52" t="s">
         <v>289</v>
       </c>
@@ -8336,7 +8342,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="79" t="s">
+      <c r="A221" s="86" t="s">
         <v>292</v>
       </c>
       <c r="B221" s="49" t="s">
@@ -8344,13 +8350,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="81"/>
+      <c r="A222" s="88"/>
       <c r="B222" s="52" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="79" t="s">
+      <c r="A223" s="86" t="s">
         <v>295</v>
       </c>
       <c r="B223" s="49" t="s">
@@ -8358,31 +8364,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="80"/>
+      <c r="A224" s="87"/>
       <c r="B224" s="50" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="80"/>
+      <c r="A225" s="87"/>
       <c r="B225" s="50" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="80"/>
+      <c r="A226" s="87"/>
       <c r="B226" s="50" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="81"/>
+      <c r="A227" s="88"/>
       <c r="B227" s="52" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="79" t="s">
+      <c r="A228" s="86" t="s">
         <v>301</v>
       </c>
       <c r="B228" s="49" t="s">
@@ -8390,31 +8396,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="80"/>
+      <c r="A229" s="87"/>
       <c r="B229" s="50" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="80"/>
+      <c r="A230" s="87"/>
       <c r="B230" s="50" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="80"/>
+      <c r="A231" s="87"/>
       <c r="B231" s="50" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="80"/>
+      <c r="A232" s="87"/>
       <c r="B232" s="50" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="81"/>
+      <c r="A233" s="88"/>
       <c r="B233" s="52" t="s">
         <v>307</v>
       </c>
@@ -8428,16 +8434,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="99" t="s">
+      <c r="A236" s="81" t="s">
         <v>310</v>
       </c>
-      <c r="B236" s="98"/>
+      <c r="B236" s="80"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="97" t="s">
+      <c r="A239" s="79" t="s">
         <v>311</v>
       </c>
-      <c r="B239" s="98"/>
+      <c r="B239" s="80"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="47"/>
@@ -8536,10 +8542,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="100" t="s">
+      <c r="A257" s="82" t="s">
         <v>328</v>
       </c>
-      <c r="B257" s="101"/>
+      <c r="B257" s="83"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="47"/>
@@ -8716,10 +8722,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="86" t="s">
+      <c r="A288" s="89" t="s">
         <v>358</v>
       </c>
-      <c r="B288" s="87"/>
+      <c r="B288" s="90"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="55"/>
@@ -8910,6 +8916,30 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A288:B288"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A46"/>
+    <mergeCell ref="A47:A56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A60:A65"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="A72:A88"/>
+    <mergeCell ref="A89:A94"/>
+    <mergeCell ref="A95:A101"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="A236:B236"/>
@@ -8926,30 +8956,6 @@
     <mergeCell ref="A199:A200"/>
     <mergeCell ref="A201:A203"/>
     <mergeCell ref="A204:A207"/>
-    <mergeCell ref="A288:B288"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A46"/>
-    <mergeCell ref="A47:A56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A60:A65"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="A72:A88"/>
-    <mergeCell ref="A89:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8969,10 +8975,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="102" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="112"/>
+      <c r="B1" s="103"/>
     </row>
     <row r="2" spans="1:2" s="15" customFormat="1" ht="14.25">
       <c r="A2" s="18" t="s">
@@ -8986,7 +8992,7 @@
       <c r="A3" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="104" t="s">
         <v>1</v>
       </c>
     </row>
@@ -8994,25 +9000,25 @@
       <c r="A4" s="21" t="s">
         <v>394</v>
       </c>
-      <c r="B4" s="106"/>
+      <c r="B4" s="105"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="106"/>
+      <c r="B5" s="105"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="107"/>
+      <c r="B6" s="106"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="105" t="s">
+      <c r="B7" s="104" t="s">
         <v>395</v>
       </c>
     </row>
@@ -9020,25 +9026,25 @@
       <c r="A8" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="106"/>
+      <c r="B8" s="105"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="106"/>
+      <c r="B9" s="105"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="B10" s="107"/>
+      <c r="B10" s="106"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="105" t="s">
+      <c r="B11" s="104" t="s">
         <v>2</v>
       </c>
     </row>
@@ -9046,85 +9052,85 @@
       <c r="A12" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="106"/>
+      <c r="B12" s="105"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="106"/>
+      <c r="B13" s="105"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="106"/>
+      <c r="B14" s="105"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="106"/>
+      <c r="B15" s="105"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="106"/>
+      <c r="B16" s="105"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="106"/>
+      <c r="B17" s="105"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="B18" s="106"/>
+      <c r="B18" s="105"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="106"/>
+      <c r="B19" s="105"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="21" t="s">
         <v>397</v>
       </c>
-      <c r="B20" s="106"/>
+      <c r="B20" s="105"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="26" t="s">
         <v>398</v>
       </c>
-      <c r="B21" s="106"/>
+      <c r="B21" s="105"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="106"/>
+      <c r="B22" s="105"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="113"/>
+      <c r="B23" s="107"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="114"/>
+      <c r="B24" s="108"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="20" t="s">
         <v>399</v>
       </c>
-      <c r="B25" s="105" t="s">
+      <c r="B25" s="104" t="s">
         <v>3</v>
       </c>
     </row>
@@ -9132,61 +9138,61 @@
       <c r="A26" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="106"/>
+      <c r="B26" s="105"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="106"/>
+      <c r="B27" s="105"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="106"/>
+      <c r="B28" s="105"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="106"/>
+      <c r="B29" s="105"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="21" t="s">
         <v>400</v>
       </c>
-      <c r="B30" s="106"/>
+      <c r="B30" s="105"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="106"/>
+      <c r="B31" s="105"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="21" t="s">
         <v>401</v>
       </c>
-      <c r="B32" s="106"/>
+      <c r="B32" s="105"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="21" t="s">
         <v>402</v>
       </c>
-      <c r="B33" s="106"/>
+      <c r="B33" s="105"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="107"/>
+      <c r="B34" s="106"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="29" t="s">
         <v>403</v>
       </c>
-      <c r="B35" s="105" t="s">
+      <c r="B35" s="104" t="s">
         <v>404</v>
       </c>
     </row>
@@ -9194,13 +9200,13 @@
       <c r="A36" s="28" t="s">
         <v>405</v>
       </c>
-      <c r="B36" s="107"/>
+      <c r="B36" s="106"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="105" t="s">
+      <c r="B37" s="104" t="s">
         <v>4</v>
       </c>
     </row>
@@ -9208,19 +9214,19 @@
       <c r="A38" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="106"/>
+      <c r="B38" s="105"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="106"/>
+      <c r="B39" s="105"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="B40" s="105" t="s">
+      <c r="B40" s="104" t="s">
         <v>407</v>
       </c>
     </row>
@@ -9228,37 +9234,37 @@
       <c r="A41" s="21" t="s">
         <v>408</v>
       </c>
-      <c r="B41" s="106"/>
+      <c r="B41" s="105"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="106"/>
+      <c r="B42" s="105"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="21" t="s">
         <v>409</v>
       </c>
-      <c r="B43" s="106"/>
+      <c r="B43" s="105"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="21" t="s">
         <v>410</v>
       </c>
-      <c r="B44" s="106"/>
+      <c r="B44" s="105"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="106"/>
+      <c r="B45" s="105"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="107"/>
+      <c r="B46" s="106"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="30" t="s">
@@ -9272,7 +9278,7 @@
       <c r="A48" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="B48" s="105" t="s">
+      <c r="B48" s="104" t="s">
         <v>411</v>
       </c>
     </row>
@@ -9280,13 +9286,13 @@
       <c r="A49" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="B49" s="107"/>
+      <c r="B49" s="106"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="105" t="s">
+      <c r="B50" s="104" t="s">
         <v>6</v>
       </c>
     </row>
@@ -9294,25 +9300,25 @@
       <c r="A51" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B51" s="106"/>
+      <c r="B51" s="105"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B52" s="106"/>
+      <c r="B52" s="105"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B53" s="106"/>
+      <c r="B53" s="105"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B54" s="107"/>
+      <c r="B54" s="106"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="30" t="s">
@@ -9326,7 +9332,7 @@
       <c r="A56" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="105" t="s">
+      <c r="B56" s="104" t="s">
         <v>8</v>
       </c>
     </row>
@@ -9334,19 +9340,19 @@
       <c r="A57" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="B57" s="106"/>
+      <c r="B57" s="105"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B58" s="107"/>
+      <c r="B58" s="106"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B59" s="105" t="s">
+      <c r="B59" s="104" t="s">
         <v>7</v>
       </c>
     </row>
@@ -9354,37 +9360,37 @@
       <c r="A60" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="B60" s="106"/>
+      <c r="B60" s="105"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="B61" s="106"/>
+      <c r="B61" s="105"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="B62" s="106"/>
+      <c r="B62" s="105"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="B63" s="106"/>
+      <c r="B63" s="105"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="B64" s="107"/>
+      <c r="B64" s="106"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="21" t="s">
         <v>414</v>
       </c>
-      <c r="B65" s="108" t="s">
+      <c r="B65" s="112" t="s">
         <v>415</v>
       </c>
     </row>
@@ -9392,26 +9398,26 @@
       <c r="A66" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="B66" s="109"/>
+      <c r="B66" s="113"/>
       <c r="E66" s="33"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="B67" s="109"/>
+      <c r="B67" s="113"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="21" t="s">
         <v>416</v>
       </c>
-      <c r="B68" s="110"/>
+      <c r="B68" s="114"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="B69" s="105" t="s">
+      <c r="B69" s="104" t="s">
         <v>9</v>
       </c>
     </row>
@@ -9419,37 +9425,37 @@
       <c r="A70" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="B70" s="106"/>
+      <c r="B70" s="105"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="B71" s="106"/>
+      <c r="B71" s="105"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B72" s="106"/>
+      <c r="B72" s="105"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B73" s="106"/>
+      <c r="B73" s="105"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="B74" s="107"/>
+      <c r="B74" s="106"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="B75" s="105" t="s">
+      <c r="B75" s="104" t="s">
         <v>10</v>
       </c>
     </row>
@@ -9457,139 +9463,139 @@
       <c r="A76" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="B76" s="106"/>
+      <c r="B76" s="105"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B77" s="106"/>
+      <c r="B77" s="105"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="B78" s="106"/>
+      <c r="B78" s="105"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B79" s="106"/>
+      <c r="B79" s="105"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="B80" s="106"/>
+      <c r="B80" s="105"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="B81" s="106"/>
+      <c r="B81" s="105"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="B82" s="106"/>
+      <c r="B82" s="105"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="B83" s="106"/>
+      <c r="B83" s="105"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B84" s="106"/>
+      <c r="B84" s="105"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B85" s="106"/>
+      <c r="B85" s="105"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="B86" s="106"/>
+      <c r="B86" s="105"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="B87" s="106"/>
+      <c r="B87" s="105"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B88" s="106"/>
+      <c r="B88" s="105"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B89" s="106"/>
+      <c r="B89" s="105"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="B90" s="106"/>
+      <c r="B90" s="105"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B91" s="106"/>
+      <c r="B91" s="105"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B92" s="106"/>
+      <c r="B92" s="105"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B93" s="106"/>
+      <c r="B93" s="105"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="B94" s="106"/>
+      <c r="B94" s="105"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="B95" s="106"/>
+      <c r="B95" s="105"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="B96" s="106"/>
+      <c r="B96" s="105"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="B97" s="106"/>
+      <c r="B97" s="105"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="B98" s="102" t="s">
+      <c r="B98" s="109" t="s">
         <v>11</v>
       </c>
     </row>
@@ -9597,37 +9603,37 @@
       <c r="A99" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="B99" s="103"/>
+      <c r="B99" s="110"/>
     </row>
     <row r="100" spans="1:2" s="16" customFormat="1">
       <c r="A100" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="B100" s="103"/>
+      <c r="B100" s="110"/>
     </row>
     <row r="101" spans="1:2" s="16" customFormat="1">
       <c r="A101" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="B101" s="103"/>
+      <c r="B101" s="110"/>
     </row>
     <row r="102" spans="1:2" s="16" customFormat="1">
       <c r="A102" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="B102" s="103"/>
+      <c r="B102" s="110"/>
     </row>
     <row r="103" spans="1:2" s="16" customFormat="1">
       <c r="A103" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="B103" s="103"/>
+      <c r="B103" s="110"/>
     </row>
     <row r="104" spans="1:2" s="16" customFormat="1">
       <c r="A104" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="B104" s="104"/>
+      <c r="B104" s="111"/>
     </row>
     <row r="105" spans="1:2" s="16" customFormat="1">
       <c r="A105" s="38" t="s">
@@ -9639,22 +9645,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussFinBondRepInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussFinBondRepInfo.xlsx
@@ -66,7 +66,6 @@
     <definedName name="X01现金">枚举值!$B$17</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -4624,27 +4623,6 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4652,6 +4630,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4678,40 +4668,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4724,6 +4702,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4731,6 +4718,18 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5433,7 +5432,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J3:J65513">
       <formula1>"01 AAA+,02 AAA,03 AAA-,04 AA+,05 AA,06 AA-,07 A+,08 A,09 A-,10 A-1,11 A-2,12 A-3,13 BBB+,14 BBB,15 BBB-,16 BB+,17 BB,18 BB-,19 B+,20 B,21 B-,22 CCC+,23 CCC,24 CCC-,25 CC+,26 CC,27 CC-,28 C+,29 C,30 C-,31 D"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="N3:N65513"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写" sqref="N2"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L65513">
       <formula1>"01 高新技术企业,99 其他"</formula1>
     </dataValidation>
@@ -5444,7 +5443,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D3:D65513">
       <formula1>"01 银行间债券市场,02 商业银行柜台市场,03 上海证券交易所,04 深圳证券交易所,05 全国中小企业股份转让系统,06 上海期货交易所,07 郑州商品交易所,08 大连商品交易所,09 中国金融期货交易所,10 上海黄金交易所,11 区域性产权/资产交易市场,12 区域性商品交易所,13 区域性贵金属交易所,14 艺术品市场,15 基金市场,16 信托市场,17 全国银行间同业拆借市场,18 上海票据交易所,99 其他交易流通场所"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="请参照“输入规则”中的具体要求填写" sqref="H3:H65513"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="请参照“输入规则”中的具体要求填写" sqref="H2"/>
     <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F65513">
       <formula1>1</formula1>
       <formula2>15</formula2>
@@ -5471,7 +5470,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>枚举值!$A$3:$E$3</xm:f>
@@ -5496,6 +5495,18 @@
           </x14:formula1>
           <xm:sqref>E1 E3:E1048576</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="请参照“输入规则”中的具体要求填写">
+          <x14:formula1>
+            <xm:f>各要素值域输入规则!$B$258:$B$286</xm:f>
+          </x14:formula1>
+          <xm:sqref>H1 H3:H1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示" prompt="请按照输入规则具体填写">
+          <x14:formula1>
+            <xm:f>各要素值域输入规则!$B$139:$B$234</xm:f>
+          </x14:formula1>
+          <xm:sqref>N1 N3:N1048576</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -5565,13 +5576,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="69"/>
+      <c r="B1" s="87"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="77" t="s">
         <v>43</v>
       </c>
       <c r="B2" s="18" t="s">
@@ -5579,25 +5590,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="81"/>
+      <c r="A3" s="78"/>
       <c r="B3" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="81"/>
+      <c r="A4" s="78"/>
       <c r="B4" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="82"/>
+      <c r="A5" s="79"/>
       <c r="B5" s="13" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="80" t="s">
         <v>48</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -5605,13 +5616,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1">
-      <c r="A7" s="84"/>
+      <c r="A7" s="81"/>
       <c r="B7" s="12" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="82" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -5619,13 +5630,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1">
-      <c r="A9" s="84"/>
+      <c r="A9" s="81"/>
       <c r="B9" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="83" t="s">
         <v>54</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5633,61 +5644,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="86"/>
+      <c r="A11" s="84"/>
       <c r="B11" s="15" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="86"/>
+      <c r="A12" s="84"/>
       <c r="B12" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="86"/>
+      <c r="A13" s="84"/>
       <c r="B13" s="15" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="86"/>
+      <c r="A14" s="84"/>
       <c r="B14" s="15" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="86"/>
+      <c r="A15" s="84"/>
       <c r="B15" s="15" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="86"/>
+      <c r="A16" s="84"/>
       <c r="B16" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="86"/>
+      <c r="A17" s="84"/>
       <c r="B17" s="15" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="86"/>
+      <c r="A18" s="84"/>
       <c r="B18" s="15" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="86"/>
+      <c r="A19" s="84"/>
       <c r="B19" s="15" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="86"/>
+      <c r="A20" s="84"/>
       <c r="B20" s="15" t="s">
         <v>65</v>
       </c>
@@ -5701,7 +5712,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="73" t="s">
+      <c r="A22" s="83" t="s">
         <v>68</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -5709,19 +5720,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="86"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="15" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="74"/>
+      <c r="A24" s="85"/>
       <c r="B24" s="13" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="73" t="s">
+      <c r="A25" s="83" t="s">
         <v>72</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -5729,67 +5740,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="86"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="15" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="86"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="86"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="10" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="86"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="10" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="86"/>
+      <c r="A30" s="84"/>
       <c r="B30" s="10" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="86"/>
+      <c r="A31" s="84"/>
       <c r="B31" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="86"/>
+      <c r="A32" s="84"/>
       <c r="B32" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="86"/>
+      <c r="A33" s="84"/>
       <c r="B33" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="86"/>
+      <c r="A34" s="84"/>
       <c r="B34" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="74"/>
+      <c r="A35" s="85"/>
       <c r="B35" s="30" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="73" t="s">
+      <c r="A36" s="83" t="s">
         <v>84</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -5797,25 +5808,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="86"/>
+      <c r="A37" s="84"/>
       <c r="B37" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="86"/>
+      <c r="A38" s="84"/>
       <c r="B38" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="74"/>
+      <c r="A39" s="85"/>
       <c r="B39" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="73" t="s">
+      <c r="A40" s="83" t="s">
         <v>89</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -5823,43 +5834,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="86"/>
+      <c r="A41" s="84"/>
       <c r="B41" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="86"/>
+      <c r="A42" s="84"/>
       <c r="B42" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="86"/>
+      <c r="A43" s="84"/>
       <c r="B43" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="86"/>
+      <c r="A44" s="84"/>
       <c r="B44" s="10" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="86"/>
+      <c r="A45" s="84"/>
       <c r="B45" s="10" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="74"/>
+      <c r="A46" s="85"/>
       <c r="B46" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="73" t="s">
+      <c r="A47" s="83" t="s">
         <v>97</v>
       </c>
       <c r="B47" s="18" t="s">
@@ -5867,61 +5878,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="86"/>
+      <c r="A48" s="84"/>
       <c r="B48" s="10" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="86"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="10" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="86"/>
+      <c r="A50" s="84"/>
       <c r="B50" s="10" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="86"/>
+      <c r="A51" s="84"/>
       <c r="B51" s="10" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="86"/>
+      <c r="A52" s="84"/>
       <c r="B52" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="86"/>
+      <c r="A53" s="84"/>
       <c r="B53" s="15" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="86"/>
+      <c r="A54" s="84"/>
       <c r="B54" s="10" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="86"/>
+      <c r="A55" s="84"/>
       <c r="B55" s="15" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="74"/>
+      <c r="A56" s="85"/>
       <c r="B56" s="13" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="73" t="s">
+      <c r="A57" s="83" t="s">
         <v>108</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -5929,19 +5940,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="86"/>
+      <c r="A58" s="84"/>
       <c r="B58" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="74"/>
+      <c r="A59" s="85"/>
       <c r="B59" s="13" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="73" t="s">
+      <c r="A60" s="83" t="s">
         <v>112</v>
       </c>
       <c r="B60" s="23" t="s">
@@ -5949,37 +5960,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="86"/>
+      <c r="A61" s="84"/>
       <c r="B61" s="10" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="86"/>
+      <c r="A62" s="84"/>
       <c r="B62" s="24" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="86"/>
+      <c r="A63" s="84"/>
       <c r="B63" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="86"/>
+      <c r="A64" s="84"/>
       <c r="B64" s="10" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="74"/>
+      <c r="A65" s="85"/>
       <c r="B65" s="17" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="73" t="s">
+      <c r="A66" s="83" t="s">
         <v>119</v>
       </c>
       <c r="B66" s="23" t="s">
@@ -5987,37 +5998,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="86"/>
+      <c r="A67" s="84"/>
       <c r="B67" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="86"/>
+      <c r="A68" s="84"/>
       <c r="B68" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="86"/>
+      <c r="A69" s="84"/>
       <c r="B69" s="10" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="86"/>
+      <c r="A70" s="84"/>
       <c r="B70" s="10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="74"/>
+      <c r="A71" s="85"/>
       <c r="B71" s="17" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="6" customFormat="1">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="83" t="s">
         <v>126</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -6025,103 +6036,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="6" customFormat="1">
-      <c r="A73" s="86"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="10" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="6" customFormat="1">
-      <c r="A74" s="86"/>
+      <c r="A74" s="84"/>
       <c r="B74" s="10" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="6" customFormat="1">
-      <c r="A75" s="86"/>
+      <c r="A75" s="84"/>
       <c r="B75" s="10" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="6" customFormat="1">
-      <c r="A76" s="86"/>
+      <c r="A76" s="84"/>
       <c r="B76" s="10" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="6" customFormat="1">
-      <c r="A77" s="86"/>
+      <c r="A77" s="84"/>
       <c r="B77" s="25" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="6" customFormat="1">
-      <c r="A78" s="86"/>
+      <c r="A78" s="84"/>
       <c r="B78" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="6" customFormat="1">
-      <c r="A79" s="86"/>
+      <c r="A79" s="84"/>
       <c r="B79" s="10" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="6" customFormat="1">
-      <c r="A80" s="86"/>
+      <c r="A80" s="84"/>
       <c r="B80" s="10" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="6" customFormat="1">
-      <c r="A81" s="86"/>
+      <c r="A81" s="84"/>
       <c r="B81" s="25" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="6" customFormat="1">
-      <c r="A82" s="86"/>
+      <c r="A82" s="84"/>
       <c r="B82" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="6" customFormat="1">
-      <c r="A83" s="86"/>
+      <c r="A83" s="84"/>
       <c r="B83" s="10" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="6" customFormat="1">
-      <c r="A84" s="86"/>
+      <c r="A84" s="84"/>
       <c r="B84" s="10" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="6" customFormat="1">
-      <c r="A85" s="86"/>
+      <c r="A85" s="84"/>
       <c r="B85" s="25" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="6" customFormat="1">
-      <c r="A86" s="86"/>
+      <c r="A86" s="84"/>
       <c r="B86" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="6" customFormat="1">
-      <c r="A87" s="86"/>
+      <c r="A87" s="84"/>
       <c r="B87" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="6" customFormat="1">
-      <c r="A88" s="74"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="13" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="6" customFormat="1">
-      <c r="A89" s="73" t="s">
+      <c r="A89" s="83" t="s">
         <v>144</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -6129,38 +6140,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="6" customFormat="1">
-      <c r="A90" s="86"/>
+      <c r="A90" s="84"/>
       <c r="B90" s="15" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="6" customFormat="1">
-      <c r="A91" s="86"/>
+      <c r="A91" s="84"/>
       <c r="B91" s="15" t="s">
         <v>147</v>
       </c>
       <c r="F91" s="31"/>
     </row>
     <row r="92" spans="1:6" s="6" customFormat="1">
-      <c r="A92" s="86"/>
+      <c r="A92" s="84"/>
       <c r="B92" s="32" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="6" customFormat="1">
-      <c r="A93" s="86"/>
+      <c r="A93" s="84"/>
       <c r="B93" s="15" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="6" customFormat="1">
-      <c r="A94" s="74"/>
+      <c r="A94" s="85"/>
       <c r="B94" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="6" customFormat="1">
-      <c r="A95" s="73" t="s">
+      <c r="A95" s="83" t="s">
         <v>151</v>
       </c>
       <c r="B95" s="26" t="s">
@@ -6168,43 +6179,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="6" customFormat="1">
-      <c r="A96" s="86"/>
+      <c r="A96" s="84"/>
       <c r="B96" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="6" customFormat="1">
-      <c r="A97" s="86"/>
+      <c r="A97" s="84"/>
       <c r="B97" s="25" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="6" customFormat="1">
-      <c r="A98" s="86"/>
+      <c r="A98" s="84"/>
       <c r="B98" s="25" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="6" customFormat="1">
-      <c r="A99" s="86"/>
+      <c r="A99" s="84"/>
       <c r="B99" s="25" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="6" customFormat="1">
-      <c r="A100" s="86"/>
+      <c r="A100" s="84"/>
       <c r="B100" s="25" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="6" customFormat="1">
-      <c r="A101" s="74"/>
+      <c r="A101" s="85"/>
       <c r="B101" s="21" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="6" customFormat="1">
-      <c r="A102" s="73" t="s">
+      <c r="A102" s="83" t="s">
         <v>159</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -6212,7 +6223,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="6" customFormat="1">
-      <c r="A103" s="74"/>
+      <c r="A103" s="85"/>
       <c r="B103" s="13" t="s">
         <v>161</v>
       </c>
@@ -6230,10 +6241,10 @@
       <c r="B105" s="16"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="68" t="s">
+      <c r="A107" s="86" t="s">
         <v>164</v>
       </c>
-      <c r="B107" s="69"/>
+      <c r="B107" s="87"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="36"/>
@@ -6404,17 +6415,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="87" t="s">
+      <c r="A137" s="71" t="s">
         <v>193</v>
       </c>
-      <c r="B137" s="88"/>
+      <c r="B137" s="72"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="89"/>
-      <c r="B138" s="90"/>
+      <c r="A138" s="73"/>
+      <c r="B138" s="74"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="75" t="s">
+      <c r="A139" s="68" t="s">
         <v>194</v>
       </c>
       <c r="B139" s="38" t="s">
@@ -6422,31 +6433,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="76"/>
+      <c r="A140" s="69"/>
       <c r="B140" s="39" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="76"/>
+      <c r="A141" s="69"/>
       <c r="B141" s="39" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="76"/>
+      <c r="A142" s="69"/>
       <c r="B142" s="39" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="77"/>
+      <c r="A143" s="70"/>
       <c r="B143" s="41" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="75" t="s">
+      <c r="A144" s="68" t="s">
         <v>200</v>
       </c>
       <c r="B144" s="38" t="s">
@@ -6454,43 +6465,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="76"/>
+      <c r="A145" s="69"/>
       <c r="B145" s="39" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="76"/>
+      <c r="A146" s="69"/>
       <c r="B146" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="76"/>
+      <c r="A147" s="69"/>
       <c r="B147" s="39" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="76"/>
+      <c r="A148" s="69"/>
       <c r="B148" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="76"/>
+      <c r="A149" s="69"/>
       <c r="B149" s="39" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="77"/>
+      <c r="A150" s="70"/>
       <c r="B150" s="41" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="75" t="s">
+      <c r="A151" s="68" t="s">
         <v>208</v>
       </c>
       <c r="B151" s="38" t="s">
@@ -6498,187 +6509,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="76"/>
+      <c r="A152" s="69"/>
       <c r="B152" s="39" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="76"/>
+      <c r="A153" s="69"/>
       <c r="B153" s="39" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="76"/>
+      <c r="A154" s="69"/>
       <c r="B154" s="39" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="76"/>
+      <c r="A155" s="69"/>
       <c r="B155" s="39" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="76"/>
+      <c r="A156" s="69"/>
       <c r="B156" s="39" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="76"/>
+      <c r="A157" s="69"/>
       <c r="B157" s="39" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="76"/>
+      <c r="A158" s="69"/>
       <c r="B158" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="76"/>
+      <c r="A159" s="69"/>
       <c r="B159" s="39" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="76"/>
+      <c r="A160" s="69"/>
       <c r="B160" s="39" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="76"/>
+      <c r="A161" s="69"/>
       <c r="B161" s="39" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="76"/>
+      <c r="A162" s="69"/>
       <c r="B162" s="39" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="76"/>
+      <c r="A163" s="69"/>
       <c r="B163" s="39" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="76"/>
+      <c r="A164" s="69"/>
       <c r="B164" s="39" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="76"/>
+      <c r="A165" s="69"/>
       <c r="B165" s="39" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="76"/>
+      <c r="A166" s="69"/>
       <c r="B166" s="39" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="76"/>
+      <c r="A167" s="69"/>
       <c r="B167" s="39" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="76"/>
+      <c r="A168" s="69"/>
       <c r="B168" s="39" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="76"/>
+      <c r="A169" s="69"/>
       <c r="B169" s="39" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="76"/>
+      <c r="A170" s="69"/>
       <c r="B170" s="39" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="76"/>
+      <c r="A171" s="69"/>
       <c r="B171" s="39" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="76"/>
+      <c r="A172" s="69"/>
       <c r="B172" s="39" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="76"/>
+      <c r="A173" s="69"/>
       <c r="B173" s="39" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="76"/>
+      <c r="A174" s="69"/>
       <c r="B174" s="39" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="76"/>
+      <c r="A175" s="69"/>
       <c r="B175" s="39" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="76"/>
+      <c r="A176" s="69"/>
       <c r="B176" s="39" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="76"/>
+      <c r="A177" s="69"/>
       <c r="B177" s="39" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="76"/>
+      <c r="A178" s="69"/>
       <c r="B178" s="39" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="76"/>
+      <c r="A179" s="69"/>
       <c r="B179" s="39" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="76"/>
+      <c r="A180" s="69"/>
       <c r="B180" s="39" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="77"/>
+      <c r="A181" s="70"/>
       <c r="B181" s="41" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="75" t="s">
+      <c r="A182" s="68" t="s">
         <v>240</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -6686,19 +6697,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="76"/>
+      <c r="A183" s="69"/>
       <c r="B183" s="39" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="77"/>
+      <c r="A184" s="70"/>
       <c r="B184" s="41" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="75" t="s">
+      <c r="A185" s="68" t="s">
         <v>244</v>
       </c>
       <c r="B185" s="38" t="s">
@@ -6706,25 +6717,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="76"/>
+      <c r="A186" s="69"/>
       <c r="B186" s="39" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="76"/>
+      <c r="A187" s="69"/>
       <c r="B187" s="39" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="77"/>
+      <c r="A188" s="70"/>
       <c r="B188" s="41" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="75" t="s">
+      <c r="A189" s="68" t="s">
         <v>249</v>
       </c>
       <c r="B189" s="38" t="s">
@@ -6732,13 +6743,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="77"/>
+      <c r="A190" s="70"/>
       <c r="B190" s="41" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="75" t="s">
+      <c r="A191" s="68" t="s">
         <v>252</v>
       </c>
       <c r="B191" s="38" t="s">
@@ -6746,49 +6757,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="76"/>
+      <c r="A192" s="69"/>
       <c r="B192" s="39" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="76"/>
+      <c r="A193" s="69"/>
       <c r="B193" s="39" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="76"/>
+      <c r="A194" s="69"/>
       <c r="B194" s="39" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="76"/>
+      <c r="A195" s="69"/>
       <c r="B195" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="76"/>
+      <c r="A196" s="69"/>
       <c r="B196" s="39" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="76"/>
+      <c r="A197" s="69"/>
       <c r="B197" s="39" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="77"/>
+      <c r="A198" s="70"/>
       <c r="B198" s="41" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="75" t="s">
+      <c r="A199" s="68" t="s">
         <v>261</v>
       </c>
       <c r="B199" s="38" t="s">
@@ -6796,13 +6807,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="77"/>
+      <c r="A200" s="70"/>
       <c r="B200" s="41" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="75" t="s">
+      <c r="A201" s="68" t="s">
         <v>264</v>
       </c>
       <c r="B201" s="38" t="s">
@@ -6810,19 +6821,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="76"/>
+      <c r="A202" s="69"/>
       <c r="B202" s="39" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="77"/>
+      <c r="A203" s="70"/>
       <c r="B203" s="41" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="75" t="s">
+      <c r="A204" s="68" t="s">
         <v>268</v>
       </c>
       <c r="B204" s="38" t="s">
@@ -6830,19 +6841,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="76"/>
+      <c r="A205" s="69"/>
       <c r="B205" s="39" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="76"/>
+      <c r="A206" s="69"/>
       <c r="B206" s="39" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="77"/>
+      <c r="A207" s="70"/>
       <c r="B207" s="41" t="s">
         <v>272</v>
       </c>
@@ -6856,7 +6867,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="75" t="s">
+      <c r="A209" s="68" t="s">
         <v>275</v>
       </c>
       <c r="B209" s="38" t="s">
@@ -6864,13 +6875,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="77"/>
+      <c r="A210" s="70"/>
       <c r="B210" s="41" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="75" t="s">
+      <c r="A211" s="68" t="s">
         <v>278</v>
       </c>
       <c r="B211" s="38" t="s">
@@ -6878,19 +6889,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="76"/>
+      <c r="A212" s="69"/>
       <c r="B212" s="39" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="77"/>
+      <c r="A213" s="70"/>
       <c r="B213" s="41" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="75" t="s">
+      <c r="A214" s="68" t="s">
         <v>282</v>
       </c>
       <c r="B214" s="38" t="s">
@@ -6898,19 +6909,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="76"/>
+      <c r="A215" s="69"/>
       <c r="B215" s="39" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="77"/>
+      <c r="A216" s="70"/>
       <c r="B216" s="41" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="75" t="s">
+      <c r="A217" s="68" t="s">
         <v>286</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -6918,13 +6929,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="76"/>
+      <c r="A218" s="69"/>
       <c r="B218" s="39" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="77"/>
+      <c r="A219" s="70"/>
       <c r="B219" s="41" t="s">
         <v>289</v>
       </c>
@@ -6938,7 +6949,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="75" t="s">
+      <c r="A221" s="68" t="s">
         <v>292</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -6946,13 +6957,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="77"/>
+      <c r="A222" s="70"/>
       <c r="B222" s="41" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="75" t="s">
+      <c r="A223" s="68" t="s">
         <v>295</v>
       </c>
       <c r="B223" s="38" t="s">
@@ -6960,31 +6971,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="76"/>
+      <c r="A224" s="69"/>
       <c r="B224" s="39" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="76"/>
+      <c r="A225" s="69"/>
       <c r="B225" s="39" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="76"/>
+      <c r="A226" s="69"/>
       <c r="B226" s="39" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="77"/>
+      <c r="A227" s="70"/>
       <c r="B227" s="41" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="75" t="s">
+      <c r="A228" s="68" t="s">
         <v>301</v>
       </c>
       <c r="B228" s="38" t="s">
@@ -6992,31 +7003,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="76"/>
+      <c r="A229" s="69"/>
       <c r="B229" s="39" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="76"/>
+      <c r="A230" s="69"/>
       <c r="B230" s="39" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="76"/>
+      <c r="A231" s="69"/>
       <c r="B231" s="39" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="76"/>
+      <c r="A232" s="69"/>
       <c r="B232" s="39" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="77"/>
+      <c r="A233" s="70"/>
       <c r="B233" s="41" t="s">
         <v>307</v>
       </c>
@@ -7030,16 +7041,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="70" t="s">
+      <c r="A236" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="B236" s="69"/>
+      <c r="B236" s="87"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="68" t="s">
+      <c r="A239" s="86" t="s">
         <v>311</v>
       </c>
-      <c r="B239" s="69"/>
+      <c r="B239" s="87"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="36"/>
@@ -7138,10 +7149,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="71" t="s">
+      <c r="A257" s="89" t="s">
         <v>328</v>
       </c>
-      <c r="B257" s="72"/>
+      <c r="B257" s="90"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="36"/>
@@ -7318,10 +7329,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="78" t="s">
+      <c r="A288" s="75" t="s">
         <v>358</v>
       </c>
-      <c r="B288" s="79"/>
+      <c r="B288" s="76"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="44"/>
@@ -7512,14 +7523,22 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A236:B236"/>
+    <mergeCell ref="A239:B239"/>
+    <mergeCell ref="A257:B257"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A139:A143"/>
+    <mergeCell ref="A144:A150"/>
+    <mergeCell ref="A151:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A203"/>
+    <mergeCell ref="A204:A207"/>
     <mergeCell ref="A288:B288"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -7536,22 +7555,14 @@
     <mergeCell ref="A72:A88"/>
     <mergeCell ref="A89:A94"/>
     <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:B107"/>
-    <mergeCell ref="A236:B236"/>
-    <mergeCell ref="A239:B239"/>
-    <mergeCell ref="A257:B257"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A139:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="A151:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A203"/>
-    <mergeCell ref="A204:A207"/>
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7571,10 +7582,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="100" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="92"/>
+      <c r="B1" s="101"/>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25">
       <c r="A2" s="7" t="s">
@@ -7588,7 +7599,7 @@
       <c r="A3" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="94" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7596,25 +7607,25 @@
       <c r="A4" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="B4" s="94"/>
+      <c r="B4" s="95"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="94"/>
+      <c r="B5" s="95"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="95"/>
+      <c r="B6" s="96"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="93" t="s">
+      <c r="B7" s="94" t="s">
         <v>395</v>
       </c>
     </row>
@@ -7622,25 +7633,25 @@
       <c r="A8" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="94"/>
+      <c r="B8" s="95"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="94"/>
+      <c r="B9" s="95"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="B10" s="95"/>
+      <c r="B10" s="96"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="94" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7648,85 +7659,85 @@
       <c r="A12" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="94"/>
+      <c r="B12" s="95"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="94"/>
+      <c r="B13" s="95"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="94"/>
+      <c r="B14" s="95"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="94"/>
+      <c r="B15" s="95"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="94"/>
+      <c r="B16" s="95"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="94"/>
+      <c r="B17" s="95"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B18" s="94"/>
+      <c r="B18" s="95"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="94"/>
+      <c r="B19" s="95"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B20" s="94"/>
+      <c r="B20" s="95"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="B21" s="94"/>
+      <c r="B21" s="95"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="94"/>
+      <c r="B22" s="95"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="96"/>
+      <c r="B23" s="102"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="97"/>
+      <c r="B24" s="103"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="B25" s="93" t="s">
+      <c r="B25" s="94" t="s">
         <v>3</v>
       </c>
     </row>
@@ -7734,61 +7745,61 @@
       <c r="A26" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="94"/>
+      <c r="B26" s="95"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="94"/>
+      <c r="B27" s="95"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="94"/>
+      <c r="B28" s="95"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="94"/>
+      <c r="B29" s="95"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="B30" s="94"/>
+      <c r="B30" s="95"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="94"/>
+      <c r="B31" s="95"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="B32" s="94"/>
+      <c r="B32" s="95"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="B33" s="94"/>
+      <c r="B33" s="95"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="95"/>
+      <c r="B34" s="96"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="B35" s="93" t="s">
+      <c r="B35" s="94" t="s">
         <v>404</v>
       </c>
     </row>
@@ -7796,13 +7807,13 @@
       <c r="A36" s="17" t="s">
         <v>405</v>
       </c>
-      <c r="B36" s="95"/>
+      <c r="B36" s="96"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="93" t="s">
+      <c r="B37" s="94" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7810,19 +7821,19 @@
       <c r="A38" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="94"/>
+      <c r="B38" s="95"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="94"/>
+      <c r="B39" s="95"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="B40" s="93" t="s">
+      <c r="B40" s="94" t="s">
         <v>407</v>
       </c>
     </row>
@@ -7830,37 +7841,37 @@
       <c r="A41" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="B41" s="94"/>
+      <c r="B41" s="95"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="94"/>
+      <c r="B42" s="95"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="B43" s="94"/>
+      <c r="B43" s="95"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="B44" s="94"/>
+      <c r="B44" s="95"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="94"/>
+      <c r="B45" s="95"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="95"/>
+      <c r="B46" s="96"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="19" t="s">
@@ -7874,7 +7885,7 @@
       <c r="A48" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B48" s="93" t="s">
+      <c r="B48" s="94" t="s">
         <v>411</v>
       </c>
     </row>
@@ -7882,13 +7893,13 @@
       <c r="A49" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B49" s="95"/>
+      <c r="B49" s="96"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="93" t="s">
+      <c r="B50" s="94" t="s">
         <v>6</v>
       </c>
     </row>
@@ -7896,25 +7907,25 @@
       <c r="A51" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B51" s="94"/>
+      <c r="B51" s="95"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B52" s="94"/>
+      <c r="B52" s="95"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B53" s="94"/>
+      <c r="B53" s="95"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B54" s="95"/>
+      <c r="B54" s="96"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
@@ -7928,7 +7939,7 @@
       <c r="A56" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="93" t="s">
+      <c r="B56" s="94" t="s">
         <v>8</v>
       </c>
     </row>
@@ -7936,19 +7947,19 @@
       <c r="A57" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B57" s="94"/>
+      <c r="B57" s="95"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="B58" s="95"/>
+      <c r="B58" s="96"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B59" s="93" t="s">
+      <c r="B59" s="94" t="s">
         <v>7</v>
       </c>
     </row>
@@ -7956,37 +7967,37 @@
       <c r="A60" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B60" s="94"/>
+      <c r="B60" s="95"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B61" s="94"/>
+      <c r="B61" s="95"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B62" s="94"/>
+      <c r="B62" s="95"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B63" s="94"/>
+      <c r="B63" s="95"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="B64" s="95"/>
+      <c r="B64" s="96"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="B65" s="101" t="s">
+      <c r="B65" s="97" t="s">
         <v>415</v>
       </c>
     </row>
@@ -7994,26 +8005,26 @@
       <c r="A66" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B66" s="102"/>
+      <c r="B66" s="98"/>
       <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B67" s="102"/>
+      <c r="B67" s="98"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="B68" s="103"/>
+      <c r="B68" s="99"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B69" s="93" t="s">
+      <c r="B69" s="94" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8021,37 +8032,37 @@
       <c r="A70" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B70" s="94"/>
+      <c r="B70" s="95"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="B71" s="94"/>
+      <c r="B71" s="95"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B72" s="94"/>
+      <c r="B72" s="95"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B73" s="94"/>
+      <c r="B73" s="95"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B74" s="95"/>
+      <c r="B74" s="96"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B75" s="93" t="s">
+      <c r="B75" s="94" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8059,139 +8070,139 @@
       <c r="A76" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B76" s="94"/>
+      <c r="B76" s="95"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B77" s="94"/>
+      <c r="B77" s="95"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B78" s="94"/>
+      <c r="B78" s="95"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B79" s="94"/>
+      <c r="B79" s="95"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B80" s="94"/>
+      <c r="B80" s="95"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B81" s="94"/>
+      <c r="B81" s="95"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B82" s="94"/>
+      <c r="B82" s="95"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B83" s="94"/>
+      <c r="B83" s="95"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B84" s="94"/>
+      <c r="B84" s="95"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B85" s="94"/>
+      <c r="B85" s="95"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="B86" s="94"/>
+      <c r="B86" s="95"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B87" s="94"/>
+      <c r="B87" s="95"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B88" s="94"/>
+      <c r="B88" s="95"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B89" s="94"/>
+      <c r="B89" s="95"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="B90" s="94"/>
+      <c r="B90" s="95"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B91" s="94"/>
+      <c r="B91" s="95"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B92" s="94"/>
+      <c r="B92" s="95"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B93" s="94"/>
+      <c r="B93" s="95"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="B94" s="94"/>
+      <c r="B94" s="95"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B95" s="94"/>
+      <c r="B95" s="95"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B96" s="94"/>
+      <c r="B96" s="95"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="B97" s="94"/>
+      <c r="B97" s="95"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="B98" s="98" t="s">
+      <c r="B98" s="91" t="s">
         <v>11</v>
       </c>
     </row>
@@ -8199,37 +8210,37 @@
       <c r="A99" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="B99" s="99"/>
+      <c r="B99" s="92"/>
     </row>
     <row r="100" spans="1:2" s="5" customFormat="1">
       <c r="A100" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="B100" s="99"/>
+      <c r="B100" s="92"/>
     </row>
     <row r="101" spans="1:2" s="5" customFormat="1">
       <c r="A101" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="B101" s="99"/>
+      <c r="B101" s="92"/>
     </row>
     <row r="102" spans="1:2" s="5" customFormat="1">
       <c r="A102" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="B102" s="99"/>
+      <c r="B102" s="92"/>
     </row>
     <row r="103" spans="1:2" s="5" customFormat="1">
       <c r="A103" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="B103" s="99"/>
+      <c r="B103" s="92"/>
     </row>
     <row r="104" spans="1:2" s="5" customFormat="1">
       <c r="A104" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B104" s="100"/>
+      <c r="B104" s="93"/>
     </row>
     <row r="105" spans="1:2" s="5" customFormat="1">
       <c r="A105" s="27" t="s">
@@ -8242,22 +8253,22 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussFinBondRepInfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetSvrBussFinBondRepInfo.xlsx
@@ -4623,6 +4623,27 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4630,18 +4651,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4668,28 +4677,40 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4702,15 +4723,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4718,18 +4730,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5436,7 +5436,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L65513">
       <formula1>"01 高新技术企业,99 其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:P65513">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O65513">
       <formula1>"01 中央国债登记结算有限责任公司,02 上海清算所,03 中国证券登记结算有限责任公司,99 其他"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="提示：" prompt="请参照“输入规则”中的具体要求填写" sqref="C2"/>
@@ -5576,13 +5576,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="42" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="87"/>
+      <c r="B1" s="69"/>
     </row>
     <row r="2" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="80" t="s">
         <v>43</v>
       </c>
       <c r="B2" s="18" t="s">
@@ -5590,25 +5590,25 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="78"/>
+      <c r="A3" s="81"/>
       <c r="B3" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="78"/>
+      <c r="A4" s="81"/>
       <c r="B4" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="79"/>
+      <c r="A5" s="82"/>
       <c r="B5" s="13" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="6" customFormat="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="83" t="s">
         <v>48</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -5616,13 +5616,13 @@
       </c>
     </row>
     <row r="7" spans="1:2" s="6" customFormat="1">
-      <c r="A7" s="81"/>
+      <c r="A7" s="84"/>
       <c r="B7" s="12" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="6" customFormat="1">
-      <c r="A8" s="82" t="s">
+      <c r="A8" s="85" t="s">
         <v>51</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -5630,13 +5630,13 @@
       </c>
     </row>
     <row r="9" spans="1:2" s="6" customFormat="1">
-      <c r="A9" s="81"/>
+      <c r="A9" s="84"/>
       <c r="B9" s="12" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="83" t="s">
+      <c r="A10" s="73" t="s">
         <v>54</v>
       </c>
       <c r="B10" s="15" t="s">
@@ -5644,61 +5644,61 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="84"/>
+      <c r="A11" s="86"/>
       <c r="B11" s="15" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="84"/>
+      <c r="A12" s="86"/>
       <c r="B12" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="84"/>
+      <c r="A13" s="86"/>
       <c r="B13" s="15" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="84"/>
+      <c r="A14" s="86"/>
       <c r="B14" s="15" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="84"/>
+      <c r="A15" s="86"/>
       <c r="B15" s="15" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="84"/>
+      <c r="A16" s="86"/>
       <c r="B16" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="84"/>
+      <c r="A17" s="86"/>
       <c r="B17" s="15" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="84"/>
+      <c r="A18" s="86"/>
       <c r="B18" s="15" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="84"/>
+      <c r="A19" s="86"/>
       <c r="B19" s="15" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="84"/>
+      <c r="A20" s="86"/>
       <c r="B20" s="15" t="s">
         <v>65</v>
       </c>
@@ -5712,7 +5712,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="73" t="s">
         <v>68</v>
       </c>
       <c r="B22" s="18" t="s">
@@ -5720,19 +5720,19 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="84"/>
+      <c r="A23" s="86"/>
       <c r="B23" s="15" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="85"/>
+      <c r="A24" s="74"/>
       <c r="B24" s="13" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="83" t="s">
+      <c r="A25" s="73" t="s">
         <v>72</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -5740,67 +5740,67 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="84"/>
+      <c r="A26" s="86"/>
       <c r="B26" s="15" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="84"/>
+      <c r="A27" s="86"/>
       <c r="B27" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="84"/>
+      <c r="A28" s="86"/>
       <c r="B28" s="10" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="84"/>
+      <c r="A29" s="86"/>
       <c r="B29" s="10" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="84"/>
+      <c r="A30" s="86"/>
       <c r="B30" s="10" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="84"/>
+      <c r="A31" s="86"/>
       <c r="B31" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="84"/>
+      <c r="A32" s="86"/>
       <c r="B32" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="84"/>
+      <c r="A33" s="86"/>
       <c r="B33" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="84"/>
+      <c r="A34" s="86"/>
       <c r="B34" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="85"/>
+      <c r="A35" s="74"/>
       <c r="B35" s="30" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="83" t="s">
+      <c r="A36" s="73" t="s">
         <v>84</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -5808,25 +5808,25 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="84"/>
+      <c r="A37" s="86"/>
       <c r="B37" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="84"/>
+      <c r="A38" s="86"/>
       <c r="B38" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="85"/>
+      <c r="A39" s="74"/>
       <c r="B39" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="83" t="s">
+      <c r="A40" s="73" t="s">
         <v>89</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -5834,43 +5834,43 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="84"/>
+      <c r="A41" s="86"/>
       <c r="B41" s="10" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="84"/>
+      <c r="A42" s="86"/>
       <c r="B42" s="10" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="84"/>
+      <c r="A43" s="86"/>
       <c r="B43" s="10" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="84"/>
+      <c r="A44" s="86"/>
       <c r="B44" s="10" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="84"/>
+      <c r="A45" s="86"/>
       <c r="B45" s="10" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="85"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="83" t="s">
+      <c r="A47" s="73" t="s">
         <v>97</v>
       </c>
       <c r="B47" s="18" t="s">
@@ -5878,61 +5878,61 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="84"/>
+      <c r="A48" s="86"/>
       <c r="B48" s="10" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="84"/>
+      <c r="A49" s="86"/>
       <c r="B49" s="10" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="84"/>
+      <c r="A50" s="86"/>
       <c r="B50" s="10" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="84"/>
+      <c r="A51" s="86"/>
       <c r="B51" s="10" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="84"/>
+      <c r="A52" s="86"/>
       <c r="B52" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="84"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="15" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="84"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="10" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="84"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="15" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="85"/>
+      <c r="A56" s="74"/>
       <c r="B56" s="13" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="83" t="s">
+      <c r="A57" s="73" t="s">
         <v>108</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -5940,19 +5940,19 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="84"/>
+      <c r="A58" s="86"/>
       <c r="B58" s="10" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="85"/>
+      <c r="A59" s="74"/>
       <c r="B59" s="13" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="83" t="s">
+      <c r="A60" s="73" t="s">
         <v>112</v>
       </c>
       <c r="B60" s="23" t="s">
@@ -5960,37 +5960,37 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="84"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="10" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="84"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="24" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="84"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="84"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="10" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="85"/>
+      <c r="A65" s="74"/>
       <c r="B65" s="17" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="83" t="s">
+      <c r="A66" s="73" t="s">
         <v>119</v>
       </c>
       <c r="B66" s="23" t="s">
@@ -5998,37 +5998,37 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="84"/>
+      <c r="A67" s="86"/>
       <c r="B67" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="84"/>
+      <c r="A68" s="86"/>
       <c r="B68" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="84"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="10" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="84"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="10" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="85"/>
+      <c r="A71" s="74"/>
       <c r="B71" s="17" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:2" s="6" customFormat="1">
-      <c r="A72" s="83" t="s">
+      <c r="A72" s="73" t="s">
         <v>126</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -6036,103 +6036,103 @@
       </c>
     </row>
     <row r="73" spans="1:2" s="6" customFormat="1">
-      <c r="A73" s="84"/>
+      <c r="A73" s="86"/>
       <c r="B73" s="10" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:2" s="6" customFormat="1">
-      <c r="A74" s="84"/>
+      <c r="A74" s="86"/>
       <c r="B74" s="10" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:2" s="6" customFormat="1">
-      <c r="A75" s="84"/>
+      <c r="A75" s="86"/>
       <c r="B75" s="10" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="76" spans="1:2" s="6" customFormat="1">
-      <c r="A76" s="84"/>
+      <c r="A76" s="86"/>
       <c r="B76" s="10" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="77" spans="1:2" s="6" customFormat="1">
-      <c r="A77" s="84"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="25" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="78" spans="1:2" s="6" customFormat="1">
-      <c r="A78" s="84"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="79" spans="1:2" s="6" customFormat="1">
-      <c r="A79" s="84"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="10" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="80" spans="1:2" s="6" customFormat="1">
-      <c r="A80" s="84"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="10" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="81" spans="1:6" s="6" customFormat="1">
-      <c r="A81" s="84"/>
+      <c r="A81" s="86"/>
       <c r="B81" s="25" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="82" spans="1:6" s="6" customFormat="1">
-      <c r="A82" s="84"/>
+      <c r="A82" s="86"/>
       <c r="B82" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:6" s="6" customFormat="1">
-      <c r="A83" s="84"/>
+      <c r="A83" s="86"/>
       <c r="B83" s="10" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:6" s="6" customFormat="1">
-      <c r="A84" s="84"/>
+      <c r="A84" s="86"/>
       <c r="B84" s="10" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:6" s="6" customFormat="1">
-      <c r="A85" s="84"/>
+      <c r="A85" s="86"/>
       <c r="B85" s="25" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:6" s="6" customFormat="1">
-      <c r="A86" s="84"/>
+      <c r="A86" s="86"/>
       <c r="B86" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="6" customFormat="1">
-      <c r="A87" s="84"/>
+      <c r="A87" s="86"/>
       <c r="B87" s="25" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:6" s="6" customFormat="1">
-      <c r="A88" s="85"/>
+      <c r="A88" s="74"/>
       <c r="B88" s="13" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="89" spans="1:6" s="6" customFormat="1">
-      <c r="A89" s="83" t="s">
+      <c r="A89" s="73" t="s">
         <v>144</v>
       </c>
       <c r="B89" s="15" t="s">
@@ -6140,38 +6140,38 @@
       </c>
     </row>
     <row r="90" spans="1:6" s="6" customFormat="1">
-      <c r="A90" s="84"/>
+      <c r="A90" s="86"/>
       <c r="B90" s="15" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:6" s="6" customFormat="1">
-      <c r="A91" s="84"/>
+      <c r="A91" s="86"/>
       <c r="B91" s="15" t="s">
         <v>147</v>
       </c>
       <c r="F91" s="31"/>
     </row>
     <row r="92" spans="1:6" s="6" customFormat="1">
-      <c r="A92" s="84"/>
+      <c r="A92" s="86"/>
       <c r="B92" s="32" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="93" spans="1:6" s="6" customFormat="1">
-      <c r="A93" s="84"/>
+      <c r="A93" s="86"/>
       <c r="B93" s="15" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="94" spans="1:6" s="6" customFormat="1">
-      <c r="A94" s="85"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:6" s="6" customFormat="1">
-      <c r="A95" s="83" t="s">
+      <c r="A95" s="73" t="s">
         <v>151</v>
       </c>
       <c r="B95" s="26" t="s">
@@ -6179,43 +6179,43 @@
       </c>
     </row>
     <row r="96" spans="1:6" s="6" customFormat="1">
-      <c r="A96" s="84"/>
+      <c r="A96" s="86"/>
       <c r="B96" s="25" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="97" spans="1:2" s="6" customFormat="1">
-      <c r="A97" s="84"/>
+      <c r="A97" s="86"/>
       <c r="B97" s="25" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="98" spans="1:2" s="6" customFormat="1">
-      <c r="A98" s="84"/>
+      <c r="A98" s="86"/>
       <c r="B98" s="25" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="99" spans="1:2" s="6" customFormat="1">
-      <c r="A99" s="84"/>
+      <c r="A99" s="86"/>
       <c r="B99" s="25" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="100" spans="1:2" s="6" customFormat="1">
-      <c r="A100" s="84"/>
+      <c r="A100" s="86"/>
       <c r="B100" s="25" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="101" spans="1:2" s="6" customFormat="1">
-      <c r="A101" s="85"/>
+      <c r="A101" s="74"/>
       <c r="B101" s="21" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="102" spans="1:2" s="6" customFormat="1">
-      <c r="A102" s="83" t="s">
+      <c r="A102" s="73" t="s">
         <v>159</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -6223,7 +6223,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" s="6" customFormat="1">
-      <c r="A103" s="85"/>
+      <c r="A103" s="74"/>
       <c r="B103" s="13" t="s">
         <v>161</v>
       </c>
@@ -6241,10 +6241,10 @@
       <c r="B105" s="16"/>
     </row>
     <row r="107" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A107" s="86" t="s">
+      <c r="A107" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="B107" s="87"/>
+      <c r="B107" s="69"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="36"/>
@@ -6415,17 +6415,17 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="71" t="s">
+      <c r="A137" s="87" t="s">
         <v>193</v>
       </c>
-      <c r="B137" s="72"/>
+      <c r="B137" s="88"/>
     </row>
     <row r="138" spans="1:2" ht="81.75" customHeight="1">
-      <c r="A138" s="73"/>
-      <c r="B138" s="74"/>
+      <c r="A138" s="89"/>
+      <c r="B138" s="90"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="68" t="s">
+      <c r="A139" s="75" t="s">
         <v>194</v>
       </c>
       <c r="B139" s="38" t="s">
@@ -6433,31 +6433,31 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="69"/>
+      <c r="A140" s="76"/>
       <c r="B140" s="39" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="69"/>
+      <c r="A141" s="76"/>
       <c r="B141" s="39" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="69"/>
+      <c r="A142" s="76"/>
       <c r="B142" s="39" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="70"/>
+      <c r="A143" s="77"/>
       <c r="B143" s="41" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="68" t="s">
+      <c r="A144" s="75" t="s">
         <v>200</v>
       </c>
       <c r="B144" s="38" t="s">
@@ -6465,43 +6465,43 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="69"/>
+      <c r="A145" s="76"/>
       <c r="B145" s="39" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="69"/>
+      <c r="A146" s="76"/>
       <c r="B146" s="39" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="69"/>
+      <c r="A147" s="76"/>
       <c r="B147" s="39" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="69"/>
+      <c r="A148" s="76"/>
       <c r="B148" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="69"/>
+      <c r="A149" s="76"/>
       <c r="B149" s="39" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="70"/>
+      <c r="A150" s="77"/>
       <c r="B150" s="41" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="68" t="s">
+      <c r="A151" s="75" t="s">
         <v>208</v>
       </c>
       <c r="B151" s="38" t="s">
@@ -6509,187 +6509,187 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="69"/>
+      <c r="A152" s="76"/>
       <c r="B152" s="39" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="69"/>
+      <c r="A153" s="76"/>
       <c r="B153" s="39" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="69"/>
+      <c r="A154" s="76"/>
       <c r="B154" s="39" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="69"/>
+      <c r="A155" s="76"/>
       <c r="B155" s="39" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="69"/>
+      <c r="A156" s="76"/>
       <c r="B156" s="39" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="69"/>
+      <c r="A157" s="76"/>
       <c r="B157" s="39" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="69"/>
+      <c r="A158" s="76"/>
       <c r="B158" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="69"/>
+      <c r="A159" s="76"/>
       <c r="B159" s="39" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="69"/>
+      <c r="A160" s="76"/>
       <c r="B160" s="39" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="69"/>
+      <c r="A161" s="76"/>
       <c r="B161" s="39" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="69"/>
+      <c r="A162" s="76"/>
       <c r="B162" s="39" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="69"/>
+      <c r="A163" s="76"/>
       <c r="B163" s="39" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="69"/>
+      <c r="A164" s="76"/>
       <c r="B164" s="39" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="69"/>
+      <c r="A165" s="76"/>
       <c r="B165" s="39" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="69"/>
+      <c r="A166" s="76"/>
       <c r="B166" s="39" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="69"/>
+      <c r="A167" s="76"/>
       <c r="B167" s="39" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="69"/>
+      <c r="A168" s="76"/>
       <c r="B168" s="39" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="69"/>
+      <c r="A169" s="76"/>
       <c r="B169" s="39" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="69"/>
+      <c r="A170" s="76"/>
       <c r="B170" s="39" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="69"/>
+      <c r="A171" s="76"/>
       <c r="B171" s="39" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="69"/>
+      <c r="A172" s="76"/>
       <c r="B172" s="39" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="69"/>
+      <c r="A173" s="76"/>
       <c r="B173" s="39" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="69"/>
+      <c r="A174" s="76"/>
       <c r="B174" s="39" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="69"/>
+      <c r="A175" s="76"/>
       <c r="B175" s="39" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="69"/>
+      <c r="A176" s="76"/>
       <c r="B176" s="39" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="69"/>
+      <c r="A177" s="76"/>
       <c r="B177" s="39" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="69"/>
+      <c r="A178" s="76"/>
       <c r="B178" s="39" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="69"/>
+      <c r="A179" s="76"/>
       <c r="B179" s="39" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="69"/>
+      <c r="A180" s="76"/>
       <c r="B180" s="39" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="70"/>
+      <c r="A181" s="77"/>
       <c r="B181" s="41" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="68" t="s">
+      <c r="A182" s="75" t="s">
         <v>240</v>
       </c>
       <c r="B182" s="38" t="s">
@@ -6697,19 +6697,19 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="69"/>
+      <c r="A183" s="76"/>
       <c r="B183" s="39" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="70"/>
+      <c r="A184" s="77"/>
       <c r="B184" s="41" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="68" t="s">
+      <c r="A185" s="75" t="s">
         <v>244</v>
       </c>
       <c r="B185" s="38" t="s">
@@ -6717,25 +6717,25 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="69"/>
+      <c r="A186" s="76"/>
       <c r="B186" s="39" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="69"/>
+      <c r="A187" s="76"/>
       <c r="B187" s="39" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="70"/>
+      <c r="A188" s="77"/>
       <c r="B188" s="41" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="68" t="s">
+      <c r="A189" s="75" t="s">
         <v>249</v>
       </c>
       <c r="B189" s="38" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="70"/>
+      <c r="A190" s="77"/>
       <c r="B190" s="41" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="68" t="s">
+      <c r="A191" s="75" t="s">
         <v>252</v>
       </c>
       <c r="B191" s="38" t="s">
@@ -6757,49 +6757,49 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="69"/>
+      <c r="A192" s="76"/>
       <c r="B192" s="39" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="69"/>
+      <c r="A193" s="76"/>
       <c r="B193" s="39" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="69"/>
+      <c r="A194" s="76"/>
       <c r="B194" s="39" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="69"/>
+      <c r="A195" s="76"/>
       <c r="B195" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="69"/>
+      <c r="A196" s="76"/>
       <c r="B196" s="39" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="69"/>
+      <c r="A197" s="76"/>
       <c r="B197" s="39" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="70"/>
+      <c r="A198" s="77"/>
       <c r="B198" s="41" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="68" t="s">
+      <c r="A199" s="75" t="s">
         <v>261</v>
       </c>
       <c r="B199" s="38" t="s">
@@ -6807,13 +6807,13 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="70"/>
+      <c r="A200" s="77"/>
       <c r="B200" s="41" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="68" t="s">
+      <c r="A201" s="75" t="s">
         <v>264</v>
       </c>
       <c r="B201" s="38" t="s">
@@ -6821,19 +6821,19 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="69"/>
+      <c r="A202" s="76"/>
       <c r="B202" s="39" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="70"/>
+      <c r="A203" s="77"/>
       <c r="B203" s="41" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="68" t="s">
+      <c r="A204" s="75" t="s">
         <v>268</v>
       </c>
       <c r="B204" s="38" t="s">
@@ -6841,19 +6841,19 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="69"/>
+      <c r="A205" s="76"/>
       <c r="B205" s="39" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="69"/>
+      <c r="A206" s="76"/>
       <c r="B206" s="39" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="70"/>
+      <c r="A207" s="77"/>
       <c r="B207" s="41" t="s">
         <v>272</v>
       </c>
@@ -6867,7 +6867,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="68" t="s">
+      <c r="A209" s="75" t="s">
         <v>275</v>
       </c>
       <c r="B209" s="38" t="s">
@@ -6875,13 +6875,13 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="70"/>
+      <c r="A210" s="77"/>
       <c r="B210" s="41" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="68" t="s">
+      <c r="A211" s="75" t="s">
         <v>278</v>
       </c>
       <c r="B211" s="38" t="s">
@@ -6889,19 +6889,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="69"/>
+      <c r="A212" s="76"/>
       <c r="B212" s="39" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="70"/>
+      <c r="A213" s="77"/>
       <c r="B213" s="41" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="68" t="s">
+      <c r="A214" s="75" t="s">
         <v>282</v>
       </c>
       <c r="B214" s="38" t="s">
@@ -6909,19 +6909,19 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="69"/>
+      <c r="A215" s="76"/>
       <c r="B215" s="39" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="70"/>
+      <c r="A216" s="77"/>
       <c r="B216" s="41" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="68" t="s">
+      <c r="A217" s="75" t="s">
         <v>286</v>
       </c>
       <c r="B217" s="38" t="s">
@@ -6929,13 +6929,13 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="69"/>
+      <c r="A218" s="76"/>
       <c r="B218" s="39" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="70"/>
+      <c r="A219" s="77"/>
       <c r="B219" s="41" t="s">
         <v>289</v>
       </c>
@@ -6949,7 +6949,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="68" t="s">
+      <c r="A221" s="75" t="s">
         <v>292</v>
       </c>
       <c r="B221" s="38" t="s">
@@ -6957,13 +6957,13 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="70"/>
+      <c r="A222" s="77"/>
       <c r="B222" s="41" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="68" t="s">
+      <c r="A223" s="75" t="s">
         <v>295</v>
       </c>
       <c r="B223" s="38" t="s">
@@ -6971,31 +6971,31 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="69"/>
+      <c r="A224" s="76"/>
       <c r="B224" s="39" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="69"/>
+      <c r="A225" s="76"/>
       <c r="B225" s="39" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="69"/>
+      <c r="A226" s="76"/>
       <c r="B226" s="39" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="70"/>
+      <c r="A227" s="77"/>
       <c r="B227" s="41" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="68" t="s">
+      <c r="A228" s="75" t="s">
         <v>301</v>
       </c>
       <c r="B228" s="38" t="s">
@@ -7003,31 +7003,31 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="69"/>
+      <c r="A229" s="76"/>
       <c r="B229" s="39" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="69"/>
+      <c r="A230" s="76"/>
       <c r="B230" s="39" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="69"/>
+      <c r="A231" s="76"/>
       <c r="B231" s="39" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="69"/>
+      <c r="A232" s="76"/>
       <c r="B232" s="39" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="70"/>
+      <c r="A233" s="77"/>
       <c r="B233" s="41" t="s">
         <v>307</v>
       </c>
@@ -7041,16 +7041,16 @@
       </c>
     </row>
     <row r="236" spans="1:2" ht="60" customHeight="1">
-      <c r="A236" s="88" t="s">
+      <c r="A236" s="70" t="s">
         <v>310</v>
       </c>
-      <c r="B236" s="87"/>
+      <c r="B236" s="69"/>
     </row>
     <row r="239" spans="1:2" ht="60" customHeight="1">
-      <c r="A239" s="86" t="s">
+      <c r="A239" s="68" t="s">
         <v>311</v>
       </c>
-      <c r="B239" s="87"/>
+      <c r="B239" s="69"/>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" s="36"/>
@@ -7149,10 +7149,10 @@
       </c>
     </row>
     <row r="257" spans="1:2" ht="36" customHeight="1">
-      <c r="A257" s="89" t="s">
+      <c r="A257" s="71" t="s">
         <v>328</v>
       </c>
-      <c r="B257" s="90"/>
+      <c r="B257" s="72"/>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="36"/>
@@ -7329,10 +7329,10 @@
       </c>
     </row>
     <row r="288" spans="1:2" ht="22.5">
-      <c r="A288" s="75" t="s">
+      <c r="A288" s="78" t="s">
         <v>358</v>
       </c>
-      <c r="B288" s="76"/>
+      <c r="B288" s="79"/>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="44"/>
@@ -7523,6 +7523,30 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
   <mergeCells count="40">
+    <mergeCell ref="A223:A227"/>
+    <mergeCell ref="A228:A233"/>
+    <mergeCell ref="A137:B138"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A213"/>
+    <mergeCell ref="A214:A216"/>
+    <mergeCell ref="A217:A219"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A288:B288"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A46"/>
+    <mergeCell ref="A47:A56"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A60:A65"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="A72:A88"/>
+    <mergeCell ref="A89:A94"/>
+    <mergeCell ref="A95:A101"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="A236:B236"/>
@@ -7539,30 +7563,6 @@
     <mergeCell ref="A199:A200"/>
     <mergeCell ref="A201:A203"/>
     <mergeCell ref="A204:A207"/>
-    <mergeCell ref="A288:B288"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A46"/>
-    <mergeCell ref="A47:A56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A60:A65"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="A72:A88"/>
-    <mergeCell ref="A89:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A223:A227"/>
-    <mergeCell ref="A228:A233"/>
-    <mergeCell ref="A137:B138"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A213"/>
-    <mergeCell ref="A214:A216"/>
-    <mergeCell ref="A217:A219"/>
-    <mergeCell ref="A221:A222"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7582,10 +7582,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="91" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="101"/>
+      <c r="B1" s="92"/>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" ht="14.25">
       <c r="A2" s="7" t="s">
@@ -7599,7 +7599,7 @@
       <c r="A3" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="93" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7607,25 +7607,25 @@
       <c r="A4" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="B4" s="95"/>
+      <c r="B4" s="94"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="95"/>
+      <c r="B5" s="94"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="96"/>
+      <c r="B6" s="95"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="93" t="s">
         <v>395</v>
       </c>
     </row>
@@ -7633,25 +7633,25 @@
       <c r="A8" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="95"/>
+      <c r="B8" s="94"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="95"/>
+      <c r="B9" s="94"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="B10" s="96"/>
+      <c r="B10" s="95"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="93" t="s">
         <v>2</v>
       </c>
     </row>
@@ -7659,85 +7659,85 @@
       <c r="A12" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="95"/>
+      <c r="B12" s="94"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="95"/>
+      <c r="B13" s="94"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="95"/>
+      <c r="B14" s="94"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="95"/>
+      <c r="B15" s="94"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="95"/>
+      <c r="B16" s="94"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="95"/>
+      <c r="B17" s="94"/>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B18" s="95"/>
+      <c r="B18" s="94"/>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="95"/>
+      <c r="B19" s="94"/>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B20" s="95"/>
+      <c r="B20" s="94"/>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="B21" s="95"/>
+      <c r="B21" s="94"/>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="95"/>
+      <c r="B22" s="94"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="102"/>
+      <c r="B23" s="96"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="103"/>
+      <c r="B24" s="97"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="B25" s="94" t="s">
+      <c r="B25" s="93" t="s">
         <v>3</v>
       </c>
     </row>
@@ -7745,61 +7745,61 @@
       <c r="A26" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="95"/>
+      <c r="B26" s="94"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="95"/>
+      <c r="B27" s="94"/>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="95"/>
+      <c r="B28" s="94"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="95"/>
+      <c r="B29" s="94"/>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="B30" s="95"/>
+      <c r="B30" s="94"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="95"/>
+      <c r="B31" s="94"/>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="B32" s="95"/>
+      <c r="B32" s="94"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="B33" s="95"/>
+      <c r="B33" s="94"/>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="96"/>
+      <c r="B34" s="95"/>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="B35" s="94" t="s">
+      <c r="B35" s="93" t="s">
         <v>404</v>
       </c>
     </row>
@@ -7807,13 +7807,13 @@
       <c r="A36" s="17" t="s">
         <v>405</v>
       </c>
-      <c r="B36" s="96"/>
+      <c r="B36" s="95"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="94" t="s">
+      <c r="B37" s="93" t="s">
         <v>4</v>
       </c>
     </row>
@@ -7821,19 +7821,19 @@
       <c r="A38" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="95"/>
+      <c r="B38" s="94"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="95"/>
+      <c r="B39" s="94"/>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="B40" s="94" t="s">
+      <c r="B40" s="93" t="s">
         <v>407</v>
       </c>
     </row>
@@ -7841,37 +7841,37 @@
       <c r="A41" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="B41" s="95"/>
+      <c r="B41" s="94"/>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="95"/>
+      <c r="B42" s="94"/>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="B43" s="95"/>
+      <c r="B43" s="94"/>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="B44" s="95"/>
+      <c r="B44" s="94"/>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="95"/>
+      <c r="B45" s="94"/>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="96"/>
+      <c r="B46" s="95"/>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="19" t="s">
@@ -7885,7 +7885,7 @@
       <c r="A48" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B48" s="94" t="s">
+      <c r="B48" s="93" t="s">
         <v>411</v>
       </c>
     </row>
@@ -7893,13 +7893,13 @@
       <c r="A49" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B49" s="96"/>
+      <c r="B49" s="95"/>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="94" t="s">
+      <c r="B50" s="93" t="s">
         <v>6</v>
       </c>
     </row>
@@ -7907,25 +7907,25 @@
       <c r="A51" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B51" s="95"/>
+      <c r="B51" s="94"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B52" s="95"/>
+      <c r="B52" s="94"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B53" s="95"/>
+      <c r="B53" s="94"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B54" s="96"/>
+      <c r="B54" s="95"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="19" t="s">
@@ -7939,7 +7939,7 @@
       <c r="A56" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="94" t="s">
+      <c r="B56" s="93" t="s">
         <v>8</v>
       </c>
     </row>
@@ -7947,19 +7947,19 @@
       <c r="A57" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B57" s="95"/>
+      <c r="B57" s="94"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="B58" s="96"/>
+      <c r="B58" s="95"/>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B59" s="94" t="s">
+      <c r="B59" s="93" t="s">
         <v>7</v>
       </c>
     </row>
@@ -7967,37 +7967,37 @@
       <c r="A60" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B60" s="95"/>
+      <c r="B60" s="94"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B61" s="95"/>
+      <c r="B61" s="94"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B62" s="95"/>
+      <c r="B62" s="94"/>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B63" s="95"/>
+      <c r="B63" s="94"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="B64" s="96"/>
+      <c r="B64" s="95"/>
     </row>
     <row r="65" spans="1:5" ht="13.5" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="B65" s="97" t="s">
+      <c r="B65" s="101" t="s">
         <v>415</v>
       </c>
     </row>
@@ -8005,26 +8005,26 @@
       <c r="A66" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B66" s="98"/>
+      <c r="B66" s="102"/>
       <c r="E66" s="22"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B67" s="98"/>
+      <c r="B67" s="102"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="B68" s="99"/>
+      <c r="B68" s="103"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B69" s="94" t="s">
+      <c r="B69" s="93" t="s">
         <v>9</v>
       </c>
     </row>
@@ -8032,37 +8032,37 @@
       <c r="A70" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B70" s="95"/>
+      <c r="B70" s="94"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="B71" s="95"/>
+      <c r="B71" s="94"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B72" s="95"/>
+      <c r="B72" s="94"/>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B73" s="95"/>
+      <c r="B73" s="94"/>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B74" s="96"/>
+      <c r="B74" s="95"/>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B75" s="94" t="s">
+      <c r="B75" s="93" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8070,139 +8070,139 @@
       <c r="A76" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B76" s="95"/>
+      <c r="B76" s="94"/>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="B77" s="95"/>
+      <c r="B77" s="94"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B78" s="95"/>
+      <c r="B78" s="94"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B79" s="95"/>
+      <c r="B79" s="94"/>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B80" s="95"/>
+      <c r="B80" s="94"/>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B81" s="95"/>
+      <c r="B81" s="94"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B82" s="95"/>
+      <c r="B82" s="94"/>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B83" s="95"/>
+      <c r="B83" s="94"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B84" s="95"/>
+      <c r="B84" s="94"/>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B85" s="95"/>
+      <c r="B85" s="94"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="B86" s="95"/>
+      <c r="B86" s="94"/>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B87" s="95"/>
+      <c r="B87" s="94"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B88" s="95"/>
+      <c r="B88" s="94"/>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B89" s="95"/>
+      <c r="B89" s="94"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="B90" s="95"/>
+      <c r="B90" s="94"/>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B91" s="95"/>
+      <c r="B91" s="94"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B92" s="95"/>
+      <c r="B92" s="94"/>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B93" s="95"/>
+      <c r="B93" s="94"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="B94" s="95"/>
+      <c r="B94" s="94"/>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B95" s="95"/>
+      <c r="B95" s="94"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B96" s="95"/>
+      <c r="B96" s="94"/>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="B97" s="95"/>
+      <c r="B97" s="94"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="B98" s="91" t="s">
+      <c r="B98" s="98" t="s">
         <v>11</v>
       </c>
     </row>
@@ -8210,37 +8210,37 @@
       <c r="A99" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="B99" s="92"/>
+      <c r="B99" s="99"/>
     </row>
     <row r="100" spans="1:2" s="5" customFormat="1">
       <c r="A100" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="B100" s="92"/>
+      <c r="B100" s="99"/>
     </row>
     <row r="101" spans="1:2" s="5" customFormat="1">
       <c r="A101" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="B101" s="92"/>
+      <c r="B101" s="99"/>
     </row>
     <row r="102" spans="1:2" s="5" customFormat="1">
       <c r="A102" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="B102" s="92"/>
+      <c r="B102" s="99"/>
     </row>
     <row r="103" spans="1:2" s="5" customFormat="1">
       <c r="A103" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="B103" s="92"/>
+      <c r="B103" s="99"/>
     </row>
     <row r="104" spans="1:2" s="5" customFormat="1">
       <c r="A104" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="B104" s="93"/>
+      <c r="B104" s="100"/>
     </row>
     <row r="105" spans="1:2" s="5" customFormat="1">
       <c r="A105" s="27" t="s">
@@ -8253,22 +8253,22 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B24"/>
-    <mergeCell ref="B25:B34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B54"/>
     <mergeCell ref="B98:B104"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="B59:B64"/>
     <mergeCell ref="B65:B68"/>
     <mergeCell ref="B69:B74"/>
     <mergeCell ref="B75:B97"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B24"/>
+    <mergeCell ref="B25:B34"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
